--- a/reports/meta-llama_Llama-3.3-70B-Instruct.xlsx
+++ b/reports/meta-llama_Llama-3.3-70B-Instruct.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08 13:58:42</t>
+          <t>2026-03-10 18:41:21</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4/12 (33.3%)</t>
+          <t>5/12 (41.7%)</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4/12 (33.3%)</t>
+          <t>5/12 (41.7%)</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0/10 (0.0%)</t>
+          <t>3/10 (30.0%)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12/34 (35.3%)</t>
+          <t>13/34 (38.2%)</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16/30 (53.3%)</t>
+          <t>18/30 (60.0%)</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12/25 (48.0%)</t>
+          <t>14/25 (56.0%)</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17/25 (68.0%)</t>
+          <t>19/25 (76.0%)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4/13 (30.8%)</t>
+          <t>6/13 (46.2%)</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4/15 (26.7%)</t>
+          <t>7/15 (46.7%)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>47/83 (56.6%)</t>
+          <t>53/83 (63.9%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31/74 (41.9%)</t>
+          <t>40/74 (54.1%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9/37 (24.3%)</t>
+          <t>11/37 (29.7%)</t>
         </is>
       </c>
     </row>
@@ -1233,9 +1233,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1817,9 +1817,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2909,9 +2909,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3020,9 +3020,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3057,9 +3057,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3363,9 +3363,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4079,9 +4079,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4571,9 +4571,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4608,9 +4608,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5592,9 +5592,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5892,9 +5892,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6266,9 +6266,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6530,9 +6530,9 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6757,9 +6757,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7093,9 +7093,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7130,9 +7130,9 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7776,9 +7776,9 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9278,9 +9278,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -10317,9 +10317,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -12328,9 +12328,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B367" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B367" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -12553,9 +12553,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B388" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B388" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -12628,9 +12628,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B395" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B395" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -13210,9 +13210,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B451" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B451" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -14536,9 +14536,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B584" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B584" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15420,9 +15420,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B675" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B675" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -15487,9 +15487,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B682" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B682" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -17265,9 +17265,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B864" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B864" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -17813,9 +17813,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B920" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B920" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -18498,9 +18498,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B990" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B990" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -18985,9 +18985,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1039" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1039" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -19402,9 +19402,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1081" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1081" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -20008,9 +20008,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1144" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1144" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -20075,9 +20075,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1151" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1151" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -21267,9 +21267,9 @@
           <t>Result:</t>
         </is>
       </c>
-      <c r="B1270" s="11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="B1270" s="12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
